--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011CAFF6-CB54-4598-8D3F-E8349F92CB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27ABF11-50E0-4408-9660-64ED4251C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,23 +269,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,8 +579,8 @@
     <col min="8" max="8" width="11.75" customWidth="1"/>
     <col min="9" max="9" width="4.75" customWidth="1"/>
     <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-    <col min="12" max="12" width="17.625" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="9.375" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="15" max="16" width="12.75" customWidth="1"/>
     <col min="17" max="17" width="15.25" customWidth="1"/>
@@ -609,30 +609,30 @@
       <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="Z1" s="8" t="s">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="Z1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -650,30 +650,30 @@
       <c r="E2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="Z2" s="6" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="Z2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -713,29 +713,29 @@
       <c r="H4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
       <c r="Z4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AA4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -750,17 +750,17 @@
       <c r="H5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -769,18 +769,18 @@
       <c r="I6" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5" t="s">
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -789,18 +789,18 @@
       <c r="I7" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -809,19 +809,19 @@
       <c r="J8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
       <c r="N8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.2">
@@ -852,19 +852,19 @@
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
         <v>23</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="1">
@@ -887,19 +887,19 @@
       <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" t="s">
         <v>24</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="P10" s="1">
@@ -925,19 +925,19 @@
       <c r="J11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
         <v>24</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="P11" s="1">
@@ -951,15 +951,18 @@
       <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12" t="s">
         <v>23</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="L13" s="3"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="Q15" s="4"/>
@@ -972,20 +975,13 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="12:19" x14ac:dyDescent="0.2">
-      <c r="L17" s="3"/>
+    <row r="17" spans="17:19" x14ac:dyDescent="0.2">
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="S4:U4"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="N7:Q7"/>
     <mergeCell ref="K8:M8"/>
@@ -996,6 +992,12 @@
     <mergeCell ref="J6:M6"/>
     <mergeCell ref="I4:Q4"/>
     <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="S4:U4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27ABF11-50E0-4408-9660-64ED4251C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE1C32-21B2-4A45-94F5-D1397E0A4044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,6 +196,14 @@
   </si>
   <si>
     <t>负面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>捣蛋鬼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他人很讨厌这家伙！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -272,20 +280,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,30 +617,30 @@
       <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="Z1" s="6" t="s">
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="Z1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -650,20 +658,20 @@
       <c r="E2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -725,17 +733,17 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="3"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
       <c r="Z4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="8" t="s">
+      <c r="AA4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -750,17 +758,17 @@
       <c r="H5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -769,18 +777,18 @@
       <c r="I6" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9" t="s">
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -789,18 +797,18 @@
       <c r="I7" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9" t="s">
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -919,6 +927,15 @@
       <c r="E11" t="s">
         <v>30</v>
       </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
       <c r="I11">
         <v>1</v>
       </c>
@@ -945,6 +962,15 @@
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
       <c r="I12">
         <v>2</v>
       </c>
@@ -960,8 +986,26 @@
       <c r="M12" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
       <c r="L13" s="3"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.2">
@@ -982,6 +1026,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="S4:U4"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="N7:Q7"/>
     <mergeCell ref="K8:M8"/>
@@ -992,12 +1042,6 @@
     <mergeCell ref="J6:M6"/>
     <mergeCell ref="I4:Q4"/>
     <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="S4:U4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE1C32-21B2-4A45-94F5-D1397E0A4044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7947721-AB44-4DE2-8E6E-BCB47F61968C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,46 @@
   </si>
   <si>
     <t>其他人很讨厌这家伙！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>慷慨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你满足他的所有要求，他会给你金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>signedValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满足所有要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;size=50&gt;获得2金币&lt;/size&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition_当前顾客要求全满足</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_获得金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -575,33 +615,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="7.375" customWidth="1"/>
-    <col min="7" max="7" width="10.125" customWidth="1"/>
-    <col min="8" max="8" width="11.75" customWidth="1"/>
-    <col min="9" max="9" width="4.75" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="15" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="15.25" customWidth="1"/>
-    <col min="18" max="18" width="21" customWidth="1"/>
-    <col min="19" max="19" width="15.25" customWidth="1"/>
-    <col min="20" max="21" width="15.625" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="21.125" customWidth="1"/>
-    <col min="24" max="24" width="24.25" customWidth="1"/>
-    <col min="25" max="25" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="9.125" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="7.375" customWidth="1"/>
+    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="10" max="10" width="4.75" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="9.375" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="16" max="17" width="12.75" customWidth="1"/>
+    <col min="18" max="18" width="15.25" customWidth="1"/>
+    <col min="19" max="19" width="21" customWidth="1"/>
+    <col min="20" max="20" width="15.25" customWidth="1"/>
+    <col min="21" max="22" width="15.625" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="21.125" customWidth="1"/>
+    <col min="25" max="25" width="24.25" customWidth="1"/>
+    <col min="26" max="26" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -615,12 +656,14 @@
         <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
@@ -631,18 +674,19 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
+      <c r="R1" s="8"/>
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
-      <c r="Z1" s="9" t="s">
+      <c r="V1" s="9"/>
+      <c r="AA1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" s="9"/>
       <c r="AB1" s="9"/>
       <c r="AC1" s="9"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD1" s="9"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -655,13 +699,15 @@
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
@@ -672,18 +718,19 @@
       <c r="O2" s="8"/>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="7"/>
+      <c r="R2" s="8"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
-      <c r="Z2" s="7" t="s">
+      <c r="V2" s="7"/>
+      <c r="AA2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD2" s="7"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -696,7 +743,9 @@
       <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -705,26 +754,26 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="Z3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="AA3" s="1"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB3" s="1"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
@@ -732,36 +781,36 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="10"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="3"/>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
-      <c r="Z4" s="3" t="s">
+      <c r="V4" s="10"/>
+      <c r="AA4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="10" t="s">
+      <c r="AB4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="AB4" s="10"/>
       <c r="AC4" s="10"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD4" s="10"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -769,70 +818,71 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="6"/>
+      <c r="O6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="R6" s="6"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="6"/>
+      <c r="O7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="7"/>
+      <c r="O8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="P8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="R8" s="7"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
@@ -842,79 +892,82 @@
       <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>33</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>35</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="O9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="P9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F10" t="s">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>36</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>2</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="P10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2</v>
       </c>
@@ -924,79 +977,85 @@
       <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>42</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>35</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>24</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="O11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="P11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="F12" t="s">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
         <v>41</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>36</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>2</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="O12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="P12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
       <c r="B13">
         <v>3</v>
       </c>
@@ -1006,42 +1065,90 @@
       <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="Q15" s="4"/>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="Q16" s="1"/>
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-    </row>
-    <row r="17" spans="17:19" x14ac:dyDescent="0.2">
-      <c r="Q17" s="4"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="5:20" x14ac:dyDescent="0.2">
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+    </row>
+    <row r="20" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="Z2:AC2"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="F1:Q1"/>
-    <mergeCell ref="F2:Q2"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="I4:Q4"/>
-    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="AB4:AD4"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="G1:R1"/>
+    <mergeCell ref="G2:R2"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="J4:R4"/>
+    <mergeCell ref="J5:R5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7947721-AB44-4DE2-8E6E-BCB47F61968C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBB85A4-EEC2-43E9-A7B0-90AF5860299E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -984,10 +984,10 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
         <v>35</v>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="G12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" t="s">
         <v>36</v>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBB85A4-EEC2-43E9-A7B0-90AF5860299E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2414BA28-DB01-484F-9A98-4905F56220E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*GA_AfterRemove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>标签名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,10 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DV_值,7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不能吃太多！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>食材多于7个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;size=50&gt;1.5x&lt;/size&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,6 +232,42 @@
   </si>
   <si>
     <t>DV_值,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食材多于6个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_增加顾客等待值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机除自己,DV_值-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomerActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,CustomerCGA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串完烤串后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*actionCGAs</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -303,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -320,6 +344,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -329,11 +356,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
@@ -632,17 +659,12 @@
     <col min="13" max="13" width="9.375" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="16" max="17" width="12.75" customWidth="1"/>
-    <col min="18" max="18" width="15.25" customWidth="1"/>
-    <col min="19" max="19" width="21" customWidth="1"/>
-    <col min="20" max="20" width="15.25" customWidth="1"/>
-    <col min="21" max="22" width="15.625" customWidth="1"/>
-    <col min="23" max="23" width="12.625" customWidth="1"/>
-    <col min="24" max="24" width="21.125" customWidth="1"/>
-    <col min="25" max="25" width="24.25" customWidth="1"/>
-    <col min="26" max="26" width="20.5" customWidth="1"/>
+    <col min="18" max="18" width="12.375" style="10" customWidth="1"/>
+    <col min="19" max="19" width="7.125" customWidth="1"/>
+    <col min="20" max="25" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -656,37 +678,36 @@
         <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
-      <c r="AA1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -700,37 +721,36 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="AA2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -738,13 +758,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -752,55 +772,57 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="AA4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>1</v>
@@ -808,347 +830,431 @@
       <c r="I5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="J5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="S6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6" t="s">
+      <c r="K7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="S7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="Q8" s="8"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="V8" s="8"/>
+      <c r="W8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="P9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="R9" s="2"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="G10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J10">
         <v>2</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q10" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="R10" s="2"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="M11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q11" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="R11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="G12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
         <v>33</v>
-      </c>
-      <c r="I12" t="s">
-        <v>36</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="P12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M13" s="3"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="R13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="S13" s="11">
+        <v>2</v>
+      </c>
+      <c r="W13" t="s">
+        <v>54</v>
+      </c>
+      <c r="X13" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-    </row>
-    <row r="17" spans="5:20" x14ac:dyDescent="0.2">
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-    </row>
-    <row r="20" spans="5:20" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="AB4:AD4"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="T4:V4"/>
+  <mergeCells count="20">
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="S4:Y4"/>
+    <mergeCell ref="S5:Y5"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="W6:Y6"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O7:Q7"/>
     <mergeCell ref="L8:N8"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="G1:R1"/>
-    <mergeCell ref="G2:R2"/>
-    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="G2:Q2"/>
+    <mergeCell ref="O6:Q6"/>
     <mergeCell ref="K6:N6"/>
-    <mergeCell ref="J4:R4"/>
-    <mergeCell ref="J5:R5"/>
+    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="J5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2414BA28-DB01-484F-9A98-4905F56220E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FD632A-E1F2-4E29-AB06-77AB7CAFB6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="66">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -268,6 +268,26 @@
   </si>
   <si>
     <t>*actionCGAs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讨价还价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能会和你掰扯掰扯…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单进行时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GA_触发瞬时遭遇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bargain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1177,7 +1197,7 @@
         <v>59</v>
       </c>
       <c r="S13" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W13" t="s">
         <v>54</v>
@@ -1229,7 +1249,36 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
+        <v>64</v>
+      </c>
+      <c r="X17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
     </row>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FD632A-E1F2-4E29-AB06-77AB7CAFB6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01712140-2CD6-4A61-AC29-4176B26DDDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -251,10 +251,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>随机除自己,DV_值-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CustomerActionType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -288,6 +284,22 @@
   </si>
   <si>
     <t>bargain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开心果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家都很喜欢它</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机除自己,DV_值-99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -380,7 +392,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,7 +729,7 @@
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
       <c r="R1" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
@@ -760,7 +772,7 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
@@ -861,7 +873,7 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S5" s="7" t="s">
         <v>37</v>
@@ -1194,7 +1206,7 @@
       </c>
       <c r="M13" s="3"/>
       <c r="R13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S13" s="11">
         <v>1</v>
@@ -1206,7 +1218,7 @@
         <v>55</v>
       </c>
       <c r="Y13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -1249,15 +1261,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>5</v>
       </c>
       <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
         <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1266,19 +1278,51 @@
         <v>28</v>
       </c>
       <c r="R17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
         <v>63</v>
       </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>64</v>
       </c>
-      <c r="X17" t="s">
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="S19" s="11">
+        <v>1</v>
+      </c>
+      <c r="W19" t="s">
+        <v>54</v>
+      </c>
+      <c r="X19" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
     </row>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01712140-2CD6-4A61-AC29-4176B26DDDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977299E7-DD86-4DE0-B115-A48DE09214A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -191,10 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>其他人很讨厌这家伙！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>慷慨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -291,15 +287,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>大家都很喜欢它</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>随机除自己,DV_值-99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DV_值,-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次串完串后
+使队伍中的顾客等待值-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次串完串后
+使队伍中的顾客等待值+5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -359,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -380,19 +382,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,28 +680,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.08203125" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="9.125" customWidth="1"/>
+    <col min="5" max="5" width="9.08203125" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="7.375" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.08203125" customWidth="1"/>
+    <col min="9" max="9" width="18.58203125" customWidth="1"/>
     <col min="10" max="10" width="4.75" customWidth="1"/>
-    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="9.375" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="16" max="17" width="12.75" customWidth="1"/>
-    <col min="18" max="18" width="12.375" style="10" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" style="7" customWidth="1"/>
+    <col min="19" max="19" width="7.08203125" customWidth="1"/>
     <col min="20" max="25" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -710,36 +715,36 @@
         <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -753,36 +758,36 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -796,7 +801,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -813,7 +818,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -826,30 +831,30 @@
       <c r="I4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
       <c r="R4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -862,131 +867,131 @@
       <c r="I5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="S5" s="7" t="s">
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
       <c r="S6" t="s">
         <v>0</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7" t="s">
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7" t="s">
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
       <c r="S7" t="s">
         <v>1</v>
       </c>
-      <c r="T7" s="7" t="s">
+      <c r="T7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7" t="s">
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
       <c r="O8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Q8" s="8"/>
+      <c r="Q8" s="11"/>
       <c r="R8" s="2"/>
       <c r="S8" s="6"/>
       <c r="T8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U8" s="8" t="s">
+      <c r="U8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="V8" s="8"/>
+      <c r="V8" s="11"/>
       <c r="W8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="8" t="s">
+      <c r="X8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Y8" s="8"/>
+      <c r="Y8" s="11"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1</v>
       </c>
@@ -1044,12 +1049,12 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="G10" t="s">
         <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
@@ -1067,7 +1072,7 @@
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>21</v>
@@ -1087,7 +1092,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2</v>
       </c>
@@ -1107,7 +1112,7 @@
         <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
@@ -1125,7 +1130,7 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>21</v>
@@ -1145,7 +1150,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="G12" t="s">
         <v>39</v>
       </c>
@@ -1188,15 +1193,15 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="42" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
-        <v>41</v>
+      <c r="D13" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1205,31 +1210,31 @@
         <v>28</v>
       </c>
       <c r="M13" s="3"/>
-      <c r="R13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="S13" s="11">
+      <c r="R13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="S13" s="8">
         <v>1</v>
       </c>
       <c r="W13" t="s">
+        <v>53</v>
+      </c>
+      <c r="X13" t="s">
         <v>54</v>
       </c>
-      <c r="X13" t="s">
-        <v>55</v>
-      </c>
       <c r="Y13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1241,35 +1246,35 @@
         <v>38</v>
       </c>
       <c r="H15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
         <v>47</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="L15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>5</v>
       </c>
       <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
         <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1277,28 +1282,28 @@
       <c r="F17" t="s">
         <v>28</v>
       </c>
-      <c r="R17" s="10" t="s">
+      <c r="R17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
         <v>62</v>
       </c>
-      <c r="S17">
-        <v>1</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>63</v>
       </c>
-      <c r="X17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:25" ht="42" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1306,28 +1311,38 @@
       <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="R19" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="S19" s="11">
+      <c r="R19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="8">
         <v>1</v>
       </c>
       <c r="W19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Y19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="G1:Q1"/>
+    <mergeCell ref="G2:Q2"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="J5:Q5"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="R2:Y2"/>
@@ -1338,16 +1353,6 @@
     <mergeCell ref="S5:Y5"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="G1:Q1"/>
-    <mergeCell ref="G2:Q2"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="J5:Q5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977299E7-DD86-4DE0-B115-A48DE09214A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A3F87D-B92A-401B-99A1-DEDBD66FD221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="71">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -302,6 +302,14 @@
   <si>
     <t>每次串完串后
 使队伍中的顾客等待值+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店老板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉格斯</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -388,16 +396,16 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,33 +687,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.08203125" customWidth="1"/>
+    <col min="2" max="2" width="6" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="9.08203125" customWidth="1"/>
+    <col min="5" max="5" width="5.75" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.08203125" customWidth="1"/>
-    <col min="9" max="9" width="18.58203125" customWidth="1"/>
+    <col min="7" max="7" width="7.375" customWidth="1"/>
+    <col min="8" max="8" width="10.125" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
     <col min="10" max="10" width="4.75" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="13" max="13" width="9.375" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="16" max="17" width="12.75" customWidth="1"/>
-    <col min="18" max="18" width="12.33203125" style="7" customWidth="1"/>
-    <col min="19" max="19" width="7.08203125" customWidth="1"/>
+    <col min="18" max="18" width="12.375" style="7" customWidth="1"/>
+    <col min="19" max="19" width="7.125" customWidth="1"/>
     <col min="20" max="25" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -720,35 +728,35 @@
       <c r="F1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -763,35 +771,35 @@
       <c r="F2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10" t="s">
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -818,7 +826,7 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -854,7 +862,7 @@
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -867,94 +875,94 @@
       <c r="I5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
       <c r="R5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>0</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9" t="s">
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
       <c r="S6" t="s">
         <v>0</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="T6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9" t="s">
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9" t="s">
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
       <c r="S7" t="s">
         <v>1</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="T7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9" t="s">
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -991,8 +999,8 @@
       <c r="Y8" s="11"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B9">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B9" s="7">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -1049,7 +1057,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="G10" t="s">
         <v>39</v>
       </c>
@@ -1092,8 +1100,8 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B11">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
       <c r="C11" t="s">
@@ -1150,7 +1158,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="G12" t="s">
         <v>39</v>
       </c>
@@ -1193,14 +1201,14 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="42" x14ac:dyDescent="0.3">
-      <c r="B13">
+    <row r="13" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B13" s="7">
         <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>68</v>
       </c>
       <c r="E13">
@@ -1226,8 +1234,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B15">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B15" s="7">
         <v>4</v>
       </c>
       <c r="C15" t="s">
@@ -1266,8 +1274,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B17">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B17" s="7">
         <v>5</v>
       </c>
       <c r="C17" t="s">
@@ -1295,14 +1303,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="2:25" ht="42" x14ac:dyDescent="0.3">
-      <c r="B19">
+    <row r="19" spans="2:25" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="B19" s="7">
         <v>6</v>
       </c>
       <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E19">
@@ -1327,12 +1335,43 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
     </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B21" s="7">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B23" s="7">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="B25" s="7">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="R2:Y2"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="S4:Y4"/>
+    <mergeCell ref="S5:Y5"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="W6:Y6"/>
     <mergeCell ref="K7:N7"/>
     <mergeCell ref="O7:Q7"/>
     <mergeCell ref="L8:N8"/>
@@ -1343,16 +1382,6 @@
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="J4:Q4"/>
     <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="W7:Y7"/>
-    <mergeCell ref="R2:Y2"/>
-    <mergeCell ref="R1:Y1"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="S4:Y4"/>
-    <mergeCell ref="S5:Y5"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="W6:Y6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A3F87D-B92A-401B-99A1-DEDBD66FD221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E828C5-4478-46F3-8084-5A153B0708B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -694,11 +694,11 @@
     <col min="3" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="4" width="15.25" customWidth="1"/>
     <col min="5" max="5" width="5.75" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="7.375" customWidth="1"/>
     <col min="8" max="8" width="10.125" customWidth="1"/>
     <col min="9" max="9" width="18.625" customWidth="1"/>
-    <col min="10" max="10" width="4.75" customWidth="1"/>
+    <col min="10" max="10" width="4.75" style="7" customWidth="1"/>
     <col min="11" max="11" width="17.875" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="9.375" customWidth="1"/>
@@ -902,7 +902,7 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K6" s="10" t="s">
@@ -934,7 +934,7 @@
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="7" t="s">
         <v>1</v>
       </c>
       <c r="K7" s="10" t="s">
@@ -1024,7 +1024,7 @@
       <c r="I9" t="s">
         <v>32</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="7">
         <v>1</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -1067,7 +1067,7 @@
       <c r="I10" t="s">
         <v>33</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="7">
         <v>2</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -1125,7 +1125,7 @@
       <c r="I11" t="s">
         <v>32</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -1168,7 +1168,7 @@
       <c r="I12" t="s">
         <v>33</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>2</v>
       </c>
       <c r="K12" s="2" t="s">
@@ -1259,7 +1259,7 @@
       <c r="I15" t="s">
         <v>47</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="7">
         <v>1</v>
       </c>
       <c r="K15" s="5" t="s">

--- a/Config/Datas/CustomerTags/CustomerTag.xlsx
+++ b/Config/Datas/CustomerTags/CustomerTag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\CustomerTags\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E828C5-4478-46F3-8084-5A153B0708B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB50CE78-BE33-4035-AF48-290F582F8285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
